--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8620689655172413</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="B2">
-        <v>0.05405405405405406</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6928571428571428</v>
+        <v>0.7112676056338029</v>
       </c>
       <c r="D2">
-        <v>0.4526315789473684</v>
+        <v>0.3831775700934579</v>
       </c>
       <c r="E2">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9041095890410958</v>
+        <v>0.8961038961038961</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7112676056338029</v>
+        <v>0.704225352112676</v>
       </c>
       <c r="D2">
-        <v>0.3831775700934579</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="E2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F2">
         <v>34</v>
       </c>
       <c r="G2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
